--- a/Field/templates/template_gimokbu.xlsx
+++ b/Field/templates/template_gimokbu.xlsx
@@ -19055,10 +19055,7 @@
         </is>
       </c>
       <c r="L2" s="1828" t="n"/>
-      <c r="M2" s="869">
-        <f>입력!D17</f>
-        <v/>
-      </c>
+      <c r="M2" s="869" t="n"/>
       <c r="N2" s="1827" t="n"/>
     </row>
     <row r="3" ht="5.1" customHeight="1" s="730">
@@ -19398,10 +19395,7 @@
     </row>
     <row r="16" ht="25.9" customHeight="1" s="730">
       <c r="B16" s="1833" t="n"/>
-      <c r="C16" s="1858">
-        <f>입력!F18</f>
-        <v/>
-      </c>
+      <c r="C16" s="1858" t="n"/>
       <c r="D16" s="1835" t="n"/>
       <c r="E16" s="1859" t="n"/>
       <c r="F16" s="1835" t="n"/>
@@ -19700,90 +19694,45 @@
     </row>
     <row r="27" ht="24" customHeight="1" s="730">
       <c r="B27" s="1833" t="n"/>
-      <c r="C27" s="1883">
-        <f>IF(입력!E21="","",입력!E21)</f>
-        <v/>
-      </c>
+      <c r="C27" s="1883" t="n"/>
       <c r="D27" s="1835" t="n"/>
-      <c r="E27" s="1883">
-        <f>IF(입력!F21="","",입력!F21)</f>
-        <v/>
-      </c>
+      <c r="E27" s="1883" t="n"/>
       <c r="F27" s="1835" t="n"/>
-      <c r="G27" s="1883">
-        <f>IF(입력!G21="","",입력!G21)</f>
-        <v/>
-      </c>
+      <c r="G27" s="1883" t="n"/>
       <c r="H27" s="1835" t="n"/>
-      <c r="I27" s="1883">
-        <f>IF(입력!H21="","",입력!H21)</f>
-        <v/>
-      </c>
+      <c r="I27" s="1883" t="n"/>
       <c r="J27" s="1835" t="n"/>
-      <c r="K27" s="1883">
-        <f>IF(입력!I21="","",입력!I21)</f>
-        <v/>
-      </c>
+      <c r="K27" s="1883" t="n"/>
       <c r="L27" s="1835" t="n"/>
       <c r="M27" s="1880" t="n"/>
       <c r="N27" s="1881" t="n"/>
     </row>
     <row r="28" ht="24" customHeight="1" s="730">
       <c r="B28" s="1833" t="n"/>
-      <c r="C28" s="1883">
-        <f>IF(입력!E22="","",입력!E22)</f>
-        <v/>
-      </c>
+      <c r="C28" s="1883" t="n"/>
       <c r="D28" s="1835" t="n"/>
-      <c r="E28" s="1883">
-        <f>IF(입력!F22="","",입력!F22)</f>
-        <v/>
-      </c>
+      <c r="E28" s="1883" t="n"/>
       <c r="F28" s="1835" t="n"/>
-      <c r="G28" s="1883">
-        <f>IF(입력!G22="","",입력!G22)</f>
-        <v/>
-      </c>
+      <c r="G28" s="1883" t="n"/>
       <c r="H28" s="1835" t="n"/>
-      <c r="I28" s="1883">
-        <f>IF(입력!H22="","",입력!H22)</f>
-        <v/>
-      </c>
+      <c r="I28" s="1883" t="n"/>
       <c r="J28" s="1835" t="n"/>
-      <c r="K28" s="1883">
-        <f>IF(입력!I22="","",입력!I22)</f>
-        <v/>
-      </c>
+      <c r="K28" s="1883" t="n"/>
       <c r="L28" s="1835" t="n"/>
       <c r="M28" s="1880" t="n"/>
       <c r="N28" s="1881" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1" s="730">
       <c r="B29" s="1840" t="n"/>
-      <c r="C29" s="1883">
-        <f>IF(입력!E23="","",입력!E23)</f>
-        <v/>
-      </c>
+      <c r="C29" s="1883" t="n"/>
       <c r="D29" s="1835" t="n"/>
-      <c r="E29" s="1883">
-        <f>IF(입력!F23="","",입력!F23)</f>
-        <v/>
-      </c>
+      <c r="E29" s="1883" t="n"/>
       <c r="F29" s="1835" t="n"/>
-      <c r="G29" s="1883">
-        <f>IF(입력!G23="","",입력!G23)</f>
-        <v/>
-      </c>
+      <c r="G29" s="1883" t="n"/>
       <c r="H29" s="1835" t="n"/>
-      <c r="I29" s="1883">
-        <f>IF(입력!H23="","",입력!H23)</f>
-        <v/>
-      </c>
+      <c r="I29" s="1883" t="n"/>
       <c r="J29" s="1835" t="n"/>
-      <c r="K29" s="1883">
-        <f>IF(입력!I23="","",입력!I23)</f>
-        <v/>
-      </c>
+      <c r="K29" s="1883" t="n"/>
       <c r="L29" s="1835" t="n"/>
       <c r="M29" s="1854" t="n"/>
       <c r="N29" s="1830" t="n"/>
@@ -19872,118 +19821,46 @@
       </c>
     </row>
     <row r="33" ht="19.9" customHeight="1" s="730" thickTop="1">
-      <c r="B33" s="843">
-        <f>IF(C33="","",1)</f>
-        <v/>
-      </c>
-      <c r="C33" s="1891">
-        <f>IF(입력!D44="","",입력!C46)</f>
-        <v/>
-      </c>
+      <c r="B33" s="843" t="str"/>
+      <c r="C33" s="1891" t="str"/>
       <c r="D33" s="1892" t="n"/>
       <c r="E33" s="1893" t="n"/>
-      <c r="F33" s="86">
-        <f>IF(C33="","",VLOOKUP(C33,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G33" s="1894">
-        <f>IF(C33="","",입력!D46)</f>
-        <v/>
-      </c>
+      <c r="F33" s="86" t="str"/>
+      <c r="G33" s="1894" t="str"/>
       <c r="H33" s="1892" t="n"/>
-      <c r="I33" s="1895">
-        <f>IF(C33="","",입력!H46)</f>
-        <v/>
-      </c>
+      <c r="I33" s="1895" t="str"/>
       <c r="J33" s="1896" t="n"/>
-      <c r="K33" s="1897">
-        <f>IF(G33="","",VLOOKUP(C33,입력!C46:G95,5,FALSE))</f>
-        <v/>
-      </c>
+      <c r="K33" s="1897" t="str"/>
       <c r="L33" s="1893" t="n"/>
-      <c r="M33" s="842">
-        <f>IF(G33="","",VLOOKUP(C33,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
+      <c r="M33" s="842" t="str"/>
       <c r="N33" s="1892" t="n"/>
-      <c r="P33" s="304">
-        <f>IF(C33="","",VLOOKUP(C33,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="P33" s="304" t="str"/>
     </row>
     <row r="34" ht="19.9" customHeight="1" s="730">
-      <c r="B34" s="830">
-        <f>IF(C34="","",IF(B33=1,2,1))</f>
-        <v/>
-      </c>
-      <c r="C34" s="1898">
-        <f>IF(입력!D47="","",입력!C47)</f>
-        <v/>
-      </c>
+      <c r="B34" s="830" t="str"/>
+      <c r="C34" s="1898" t="str"/>
       <c r="E34" s="1899" t="n"/>
-      <c r="F34" s="87">
-        <f>IF(C34="","",VLOOKUP(C34,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G34" s="1900">
-        <f>IF(C34="","",입력!D47)</f>
-        <v/>
-      </c>
-      <c r="I34" s="1901">
-        <f>IF(C34="","",입력!H47)</f>
-        <v/>
-      </c>
+      <c r="F34" s="87" t="str"/>
+      <c r="G34" s="1900" t="str"/>
+      <c r="I34" s="1901" t="str"/>
       <c r="J34" s="1881" t="n"/>
-      <c r="K34" s="1902">
-        <f>IF(G34="","",VLOOKUP(C34,입력!C47:G96,5,FALSE))</f>
-        <v/>
-      </c>
+      <c r="K34" s="1902" t="str"/>
       <c r="L34" s="1899" t="n"/>
-      <c r="M34" s="829">
-        <f>IF(G34="","",VLOOKUP(C34,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P34" s="304">
-        <f>IF(C34="","",VLOOKUP(C34,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M34" s="829" t="str"/>
+      <c r="P34" s="304" t="str"/>
     </row>
     <row r="35" ht="19.9" customHeight="1" s="730">
-      <c r="B35" s="830">
-        <f>IF(C35="","",COUNTA($G$33:$G$35)-COUNTBLANK($G$33:$G$35))</f>
-        <v/>
-      </c>
-      <c r="C35" s="1898">
-        <f>IF(입력!D51="","",입력!C51)</f>
-        <v/>
-      </c>
+      <c r="B35" s="830" t="str"/>
+      <c r="C35" s="1898" t="str"/>
       <c r="E35" s="1899" t="n"/>
-      <c r="F35" s="87">
-        <f>IF(C35="","",VLOOKUP(C35,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G35" s="1900">
-        <f>IF(C35="","",입력!D51)</f>
-        <v/>
-      </c>
-      <c r="I35" s="1901">
-        <f>IF(C35="","",입력!H51)</f>
-        <v/>
-      </c>
+      <c r="F35" s="87" t="str"/>
+      <c r="G35" s="1900" t="str"/>
+      <c r="I35" s="1901" t="str"/>
       <c r="J35" s="1881" t="n"/>
-      <c r="K35" s="1902">
-        <f>IF(G35="","",VLOOKUP(C35,입력!C48:G97,5,FALSE))</f>
-        <v/>
-      </c>
+      <c r="K35" s="1902" t="str"/>
       <c r="L35" s="1899" t="n"/>
-      <c r="M35" s="829">
-        <f>IF(G35="","",VLOOKUP(C35,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P35" s="304">
-        <f>IF(C35="","",VLOOKUP(C35,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M35" s="829" t="str"/>
+      <c r="P35" s="304" t="str"/>
     </row>
     <row r="36" ht="19.9" customHeight="1" s="730">
       <c r="B36" s="830" t="n"/>
@@ -20001,780 +19878,306 @@
       </c>
     </row>
     <row r="37" ht="19.9" customHeight="1" s="730">
-      <c r="B37" s="830">
-        <f>IF(C37="","",COUNTA($G$33:$G37)-COUNTBLANK($G$33:$G37))</f>
-        <v/>
-      </c>
-      <c r="C37" s="1898">
-        <f>IF(입력!D53="","",입력!C53)</f>
-        <v/>
-      </c>
+      <c r="B37" s="830" t="str"/>
+      <c r="C37" s="1898" t="str"/>
       <c r="E37" s="1899" t="n"/>
-      <c r="F37" s="87">
-        <f>IF(C37="","",VLOOKUP(C37,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G37" s="913">
-        <f>IF(C37="","",입력!H53)</f>
-        <v/>
-      </c>
+      <c r="F37" s="87" t="str"/>
+      <c r="G37" s="913" t="str"/>
       <c r="I37" s="1903" t="n"/>
       <c r="J37" s="1881" t="n"/>
-      <c r="K37" s="1902">
-        <f>IF(G37="","",VLOOKUP(C37,입력!C50:G99,5,FALSE))</f>
-        <v/>
-      </c>
+      <c r="K37" s="1902" t="str"/>
       <c r="L37" s="1899" t="n"/>
-      <c r="M37" s="829">
-        <f>IF(G37="","",VLOOKUP(C37,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P37" s="304">
-        <f>IF(C37="","",VLOOKUP(C37,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M37" s="829" t="str"/>
+      <c r="P37" s="304" t="str"/>
     </row>
     <row r="38" ht="19.9" customHeight="1" s="730">
-      <c r="B38" s="830">
-        <f>IF(C38="","",COUNTA($G$33:$G38)-COUNTBLANK($G$33:$G38))</f>
-        <v/>
-      </c>
-      <c r="C38" s="1898">
-        <f>IF(입력!D55="","",입력!C55)</f>
-        <v/>
-      </c>
+      <c r="B38" s="830" t="str"/>
+      <c r="C38" s="1898" t="str"/>
       <c r="E38" s="1899" t="n"/>
-      <c r="F38" s="87">
-        <f>IF(C38="","",VLOOKUP(C38,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G38" s="902">
-        <f>IF(C38="","",입력!H55)</f>
-        <v/>
-      </c>
+      <c r="F38" s="87" t="str"/>
+      <c r="G38" s="902" t="str"/>
       <c r="I38" s="1904" t="n"/>
       <c r="J38" s="1881" t="n"/>
-      <c r="K38" s="1905">
-        <f>IF(G38="","",VLOOKUP(C38,입력!C51:G100,5,FALSE))</f>
-        <v/>
-      </c>
+      <c r="K38" s="1905" t="str"/>
       <c r="L38" s="1899" t="n"/>
-      <c r="M38" s="829">
-        <f>IF(G38="","",VLOOKUP(C38,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P38" s="304">
-        <f>IF(C38="","",VLOOKUP(C38,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M38" s="829" t="str"/>
+      <c r="P38" s="304" t="str"/>
     </row>
     <row r="39" ht="19.9" customHeight="1" s="730">
-      <c r="B39" s="830">
-        <f>IF(C39="","",COUNTA($G$33:$G39)-COUNTBLANK($G$33:$G39))</f>
-        <v/>
-      </c>
+      <c r="B39" s="830" t="str"/>
       <c r="C39" s="1898" t="n"/>
       <c r="E39" s="1899" t="n"/>
-      <c r="F39" s="87">
-        <f>IF(C39="","",VLOOKUP(C39,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G39" s="1906">
-        <f>IF(C39="","",입력!H56)</f>
-        <v/>
-      </c>
+      <c r="F39" s="87" t="str"/>
+      <c r="G39" s="1906" t="str"/>
       <c r="I39" s="1907" t="n"/>
       <c r="J39" s="1881" t="n"/>
-      <c r="K39" s="1905">
-        <f>IF(G39="","",VLOOKUP(C39,입력!C52:G101,5,FALSE))</f>
-        <v/>
-      </c>
+      <c r="K39" s="1905" t="str"/>
       <c r="L39" s="1899" t="n"/>
-      <c r="M39" s="829">
-        <f>IF(G39="","",VLOOKUP(C39,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P39" s="304">
-        <f>IF(C39="","",VLOOKUP(C39,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M39" s="829" t="str"/>
+      <c r="P39" s="304" t="str"/>
     </row>
     <row r="40" ht="19.9" customHeight="1" s="730">
-      <c r="B40" s="830">
-        <f>IF(C40="","",COUNTA($G$33:$G40)-COUNTBLANK($G$33:$G40))</f>
-        <v/>
-      </c>
-      <c r="C40" s="1898">
-        <f>IF(입력!D57="","",입력!C57)</f>
-        <v/>
-      </c>
+      <c r="B40" s="830" t="str"/>
+      <c r="C40" s="1898" t="str"/>
       <c r="E40" s="1899" t="n"/>
-      <c r="F40" s="87">
-        <f>IF(C40="","",VLOOKUP(C40,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G40" s="1906">
-        <f>IF(C40="","",입력!H57)</f>
-        <v/>
-      </c>
+      <c r="F40" s="87" t="str"/>
+      <c r="G40" s="1906" t="str"/>
       <c r="I40" s="1907" t="n"/>
       <c r="J40" s="1881" t="n"/>
-      <c r="K40" s="1908">
-        <f>IF(G40="","",VLOOKUP(C40,입력!C53:G102,5,FALSE))</f>
-        <v/>
-      </c>
+      <c r="K40" s="1908" t="str"/>
       <c r="L40" s="1899" t="n"/>
-      <c r="M40" s="829">
-        <f>IF(G40="","",VLOOKUP(C40,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P40" s="304">
-        <f>IF(C40="","",VLOOKUP(C40,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M40" s="829" t="str"/>
+      <c r="P40" s="304" t="str"/>
     </row>
     <row r="41" ht="19.9" customHeight="1" s="730">
-      <c r="B41" s="830">
-        <f>IF(C41="","",COUNTA($G$33:$G41)-COUNTBLANK($G$33:$G41))</f>
-        <v/>
-      </c>
-      <c r="C41" s="1898">
-        <f>IF(입력!D58="","",입력!C58)</f>
-        <v/>
-      </c>
+      <c r="B41" s="830" t="str"/>
+      <c r="C41" s="1898" t="str"/>
       <c r="E41" s="1899" t="n"/>
-      <c r="F41" s="87">
-        <f>IF(C41="","",VLOOKUP(C41,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G41" s="1906">
-        <f>IF(C41="","",입력!H58)</f>
-        <v/>
-      </c>
+      <c r="F41" s="87" t="str"/>
+      <c r="G41" s="1906" t="str"/>
       <c r="I41" s="1907" t="n"/>
       <c r="J41" s="1881" t="n"/>
-      <c r="K41" s="1908">
-        <f>IF(G41="","",VLOOKUP(C41,입력!C54:G103,5,FALSE))</f>
-        <v/>
-      </c>
+      <c r="K41" s="1908" t="str"/>
       <c r="L41" s="1899" t="n"/>
-      <c r="M41" s="829">
-        <f>IF(G41="","",VLOOKUP(C41,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P41" s="304">
-        <f>IF(C41="","",VLOOKUP(C41,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M41" s="829" t="str"/>
+      <c r="P41" s="304" t="str"/>
     </row>
     <row r="42" ht="19.9" customHeight="1" s="730">
-      <c r="B42" s="830">
-        <f>IF(C42="","",COUNTA($G$33:$G42)-COUNTBLANK($G$33:$G42))</f>
-        <v/>
-      </c>
-      <c r="C42" s="1898">
-        <f>IF(입력!D59="","",입력!C59)</f>
-        <v/>
-      </c>
+      <c r="B42" s="830" t="str"/>
+      <c r="C42" s="1898" t="str"/>
       <c r="E42" s="1899" t="n"/>
-      <c r="F42" s="87">
-        <f>IF(C42="","",VLOOKUP(C42,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G42" s="1906">
-        <f>IF(C42="","",입력!H59)</f>
-        <v/>
-      </c>
+      <c r="F42" s="87" t="str"/>
+      <c r="G42" s="1906" t="str"/>
       <c r="I42" s="1907" t="n"/>
       <c r="J42" s="1881" t="n"/>
-      <c r="K42" s="1908">
-        <f>IF(G42="","",VLOOKUP(C42,입력!C55:G104,5,FALSE))</f>
-        <v/>
-      </c>
+      <c r="K42" s="1908" t="str"/>
       <c r="L42" s="1899" t="n"/>
-      <c r="M42" s="829">
-        <f>IF(G42="","",VLOOKUP(C42,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P42" s="304">
-        <f>IF(C42="","",VLOOKUP(C42,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M42" s="829" t="str"/>
+      <c r="P42" s="304" t="str"/>
     </row>
     <row r="43" ht="19.9" customHeight="1" s="730">
-      <c r="B43" s="830">
-        <f>IF(C43="","",COUNTA($G$33:$G43)-COUNTBLANK($G$33:$G43))</f>
-        <v/>
-      </c>
-      <c r="C43" s="1898">
-        <f>IF(입력!D60="","",입력!C60)</f>
-        <v/>
-      </c>
+      <c r="B43" s="830" t="str"/>
+      <c r="C43" s="1898" t="str"/>
       <c r="E43" s="1899" t="n"/>
-      <c r="F43" s="87">
-        <f>IF(C43="","",VLOOKUP(C43,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G43" s="1906">
-        <f>IF(C43="","",입력!H60)</f>
-        <v/>
-      </c>
+      <c r="F43" s="87" t="str"/>
+      <c r="G43" s="1906" t="str"/>
       <c r="I43" s="1907" t="n"/>
       <c r="J43" s="1881" t="n"/>
-      <c r="K43" s="1908">
-        <f>IF(G43="","",VLOOKUP(C43,입력!C56:G105,5,FALSE))</f>
-        <v/>
-      </c>
+      <c r="K43" s="1908" t="str"/>
       <c r="L43" s="1899" t="n"/>
-      <c r="M43" s="829">
-        <f>IF(G43="","",VLOOKUP(C43,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P43" s="304">
-        <f>IF(C43="","",VLOOKUP(C43,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M43" s="829" t="str"/>
+      <c r="P43" s="304" t="str"/>
     </row>
     <row r="44" ht="19.9" customHeight="1" s="730">
-      <c r="B44" s="830">
-        <f>IF(C44="","",COUNTA($G$33:$G44)-COUNTBLANK($G$33:$G44))</f>
-        <v/>
-      </c>
-      <c r="C44" s="1898">
-        <f>IF(입력!D61="","",입력!C61)</f>
-        <v/>
-      </c>
+      <c r="B44" s="830" t="str"/>
+      <c r="C44" s="1898" t="str"/>
       <c r="E44" s="1899" t="n"/>
-      <c r="F44" s="87">
-        <f>IF(C44="","",VLOOKUP(C44,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G44" s="1906">
-        <f>IF(C44="","",입력!H61)</f>
-        <v/>
-      </c>
+      <c r="F44" s="87" t="str"/>
+      <c r="G44" s="1906" t="str"/>
       <c r="I44" s="1907" t="n"/>
       <c r="J44" s="1881" t="n"/>
-      <c r="K44" s="1909">
-        <f>IF(G44="","",VLOOKUP(C44,입력!C57:G106,5,FALSE))</f>
-        <v/>
-      </c>
+      <c r="K44" s="1909" t="str"/>
       <c r="L44" s="1899" t="n"/>
-      <c r="M44" s="829">
-        <f>IF(G44="","",VLOOKUP(C44,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P44" s="304">
-        <f>IF(C44="","",VLOOKUP(C44,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M44" s="829" t="str"/>
+      <c r="P44" s="304" t="str"/>
     </row>
     <row r="45" ht="19.9" customHeight="1" s="730">
-      <c r="B45" s="830">
-        <f>IF(C45="","",COUNTA($G$33:$G45)-COUNTBLANK($G$33:$G45))</f>
-        <v/>
-      </c>
+      <c r="B45" s="830" t="str"/>
       <c r="C45" s="1898" t="n"/>
       <c r="E45" s="1899" t="n"/>
-      <c r="F45" s="87">
-        <f>IF(C45="","",VLOOKUP(C45,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G45" s="1906">
-        <f>IF(C45="","",입력!H62)</f>
-        <v/>
-      </c>
+      <c r="F45" s="87" t="str"/>
+      <c r="G45" s="1906" t="str"/>
       <c r="I45" s="1907" t="n"/>
       <c r="J45" s="1881" t="n"/>
-      <c r="K45" s="1910">
-        <f>IF(G45="","",VLOOKUP(C45,입력!C58:G107,5,FALSE))</f>
-        <v/>
-      </c>
+      <c r="K45" s="1910" t="str"/>
       <c r="L45" s="1899" t="n"/>
-      <c r="M45" s="829">
-        <f>IF(G45="","",VLOOKUP(C45,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P45" s="304">
-        <f>IF(C45="","",VLOOKUP(C45,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M45" s="829" t="str"/>
+      <c r="P45" s="304" t="str"/>
     </row>
     <row r="46" ht="19.9" customHeight="1" s="730">
-      <c r="B46" s="830">
-        <f>IF(C46="","",COUNTA($G$33:$G46)-COUNTBLANK($G$33:$G46))</f>
-        <v/>
-      </c>
-      <c r="C46" s="1898">
-        <f>IF(입력!D63="","",입력!C63)</f>
-        <v/>
-      </c>
+      <c r="B46" s="830" t="str"/>
+      <c r="C46" s="1898" t="str"/>
       <c r="E46" s="1899" t="n"/>
-      <c r="F46" s="87">
-        <f>IF(C46="","",VLOOKUP(C46,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G46" s="1906">
-        <f>IF(C46="","",입력!H63)</f>
-        <v/>
-      </c>
+      <c r="F46" s="87" t="str"/>
+      <c r="G46" s="1906" t="str"/>
       <c r="I46" s="1907" t="n"/>
       <c r="J46" s="1881" t="n"/>
-      <c r="K46" s="1909">
-        <f>IF(G46="","",VLOOKUP(C46,입력!C59:G108,5,FALSE))</f>
-        <v/>
-      </c>
+      <c r="K46" s="1909" t="str"/>
       <c r="L46" s="1899" t="n"/>
-      <c r="M46" s="829">
-        <f>IF(G46="","",VLOOKUP(C46,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P46" s="304">
-        <f>IF(C46="","",VLOOKUP(C46,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M46" s="829" t="str"/>
+      <c r="P46" s="304" t="str"/>
     </row>
     <row r="47" ht="4.9" customHeight="1" s="730">
-      <c r="B47" s="830">
-        <f>IF(C47="","",COUNTA($G$33:$G47)-COUNTBLANK($G$33:$G47))</f>
-        <v/>
-      </c>
-      <c r="C47" s="1898">
-        <f>IF(입력!D64="","",입력!C64)</f>
-        <v/>
-      </c>
+      <c r="B47" s="830" t="str"/>
+      <c r="C47" s="1898" t="str"/>
       <c r="E47" s="1899" t="n"/>
-      <c r="F47" s="87">
-        <f>IF(C47="","",VLOOKUP(C47,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G47" s="1911">
-        <f>IF(C47="","",입력!H64)</f>
-        <v/>
-      </c>
+      <c r="F47" s="87" t="str"/>
+      <c r="G47" s="1911" t="str"/>
       <c r="H47" s="1912" t="n"/>
-      <c r="I47" s="1913">
-        <f>IF(G47="","",VLOOKUP(C47,입력!C60:G109,5,FALSE))</f>
-        <v/>
-      </c>
+      <c r="I47" s="1913" t="str"/>
       <c r="J47" s="1881" t="n"/>
       <c r="K47" s="537" t="n"/>
       <c r="L47" s="534" t="n"/>
-      <c r="M47" s="829">
-        <f>IF(G47="","",VLOOKUP(C47,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P47" s="304">
-        <f>IF(C47="","",VLOOKUP(C47,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M47" s="829" t="str"/>
+      <c r="P47" s="304" t="str"/>
     </row>
     <row r="48" ht="4.9" customHeight="1" s="730">
-      <c r="B48" s="830">
-        <f>IF(C48="","",COUNTA($G$33:$G48)-COUNTBLANK($G$33:$G48))</f>
-        <v/>
-      </c>
-      <c r="C48" s="1898">
-        <f>IF(입력!D65="","",입력!C65)</f>
-        <v/>
-      </c>
+      <c r="B48" s="830" t="str"/>
+      <c r="C48" s="1898" t="str"/>
       <c r="E48" s="1899" t="n"/>
-      <c r="F48" s="87">
-        <f>IF(C48="","",VLOOKUP(C48,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G48" s="1911">
-        <f>IF(C48="","",입력!H65)</f>
-        <v/>
-      </c>
+      <c r="F48" s="87" t="str"/>
+      <c r="G48" s="1911" t="str"/>
       <c r="H48" s="1912" t="n"/>
-      <c r="I48" s="1913">
-        <f>IF(G48="","",VLOOKUP(C48,입력!C61:G110,5,FALSE))</f>
-        <v/>
-      </c>
+      <c r="I48" s="1913" t="str"/>
       <c r="J48" s="1881" t="n"/>
       <c r="K48" s="537" t="n"/>
       <c r="L48" s="534" t="n"/>
-      <c r="M48" s="829">
-        <f>IF(G48="","",VLOOKUP(C48,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P48" s="304">
-        <f>IF(C48="","",VLOOKUP(C48,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M48" s="829" t="str"/>
+      <c r="P48" s="304" t="str"/>
     </row>
     <row r="49" ht="19.9" customHeight="1" s="730">
-      <c r="B49" s="830">
-        <f>IF(C49="","",COUNTA($G$33:$G49)-COUNTBLANK($G$33:$G49))</f>
-        <v/>
-      </c>
-      <c r="C49" s="1898">
-        <f>IF(입력!D66="","",입력!C66)</f>
-        <v/>
-      </c>
+      <c r="B49" s="830" t="str"/>
+      <c r="C49" s="1898" t="str"/>
       <c r="E49" s="1899" t="n"/>
-      <c r="F49" s="308">
-        <f>IF(C49="","",VLOOKUP(C49,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G49" s="913">
-        <f>IF(C49="","",입력!H66)</f>
-        <v/>
-      </c>
+      <c r="F49" s="308" t="str"/>
+      <c r="G49" s="913" t="str"/>
       <c r="I49" s="1903" t="n"/>
       <c r="J49" s="1881" t="n"/>
-      <c r="K49" s="1902">
-        <f>IF(G49="","",VLOOKUP(C49,입력!C63:G109,5,0))</f>
-        <v/>
-      </c>
+      <c r="K49" s="1902" t="str"/>
       <c r="L49" s="1899" t="n"/>
-      <c r="M49" s="829">
-        <f>IF(G49="","",VLOOKUP(C49,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
+      <c r="M49" s="829" t="str"/>
       <c r="P49" s="304" t="n"/>
     </row>
     <row r="50" ht="19.9" customHeight="1" s="730">
-      <c r="B50" s="830">
-        <f>IF(C50="","",COUNTA($G$33:$G50)-COUNTBLANK($G$33:$G50))</f>
-        <v/>
-      </c>
-      <c r="C50" s="1898">
-        <f>IF(입력!D68="","",입력!C68)</f>
-        <v/>
-      </c>
+      <c r="B50" s="830" t="str"/>
+      <c r="C50" s="1898" t="str"/>
       <c r="E50" s="1899" t="n"/>
-      <c r="F50" s="308">
-        <f>IF(C50="","",VLOOKUP(C50,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G50" s="902">
-        <f>IF(C50="","",입력!H68)</f>
-        <v/>
-      </c>
+      <c r="F50" s="308" t="str"/>
+      <c r="G50" s="902" t="str"/>
       <c r="I50" s="1904" t="n"/>
       <c r="J50" s="1881" t="n"/>
-      <c r="K50" s="1902">
-        <f>IF(G50="","",VLOOKUP(C50,입력!C64:G110,5,0))</f>
-        <v/>
-      </c>
+      <c r="K50" s="1902" t="str"/>
       <c r="L50" s="1899" t="n"/>
-      <c r="M50" s="829">
-        <f>IF(G50="","",VLOOKUP(C50,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P50" s="304">
-        <f>IF(C50="","",VLOOKUP(C50,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M50" s="829" t="str"/>
+      <c r="P50" s="304" t="str"/>
     </row>
     <row r="51" ht="19.9" customHeight="1" s="730">
-      <c r="B51" s="830">
-        <f>IF(C51="","",COUNTA($G$33:$G51)-COUNTBLANK($G$33:$G51))</f>
-        <v/>
-      </c>
-      <c r="C51" s="1898">
-        <f>IF(입력!D69="","",입력!C69)</f>
-        <v/>
-      </c>
+      <c r="B51" s="830" t="str"/>
+      <c r="C51" s="1898" t="str"/>
       <c r="E51" s="1899" t="n"/>
-      <c r="F51" s="308">
-        <f>IF(C51="","",VLOOKUP(C51,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G51" s="902">
-        <f>IF(C51="","",입력!H69)</f>
-        <v/>
-      </c>
+      <c r="F51" s="308" t="str"/>
+      <c r="G51" s="902" t="str"/>
       <c r="I51" s="1904" t="n"/>
       <c r="J51" s="1881" t="n"/>
-      <c r="K51" s="1902">
-        <f>IF(G51="","",VLOOKUP(C51,입력!C65:G111,5,0))</f>
-        <v/>
-      </c>
+      <c r="K51" s="1902" t="str"/>
       <c r="L51" s="1899" t="n"/>
-      <c r="M51" s="829">
-        <f>IF(G51="","",VLOOKUP(C51,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P51" s="304">
-        <f>IF(C51="","",VLOOKUP(C51,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M51" s="829" t="str"/>
+      <c r="P51" s="304" t="str"/>
     </row>
     <row r="52" ht="19.9" customHeight="1" s="730">
-      <c r="B52" s="830">
-        <f>IF(C52="","",COUNTA($G$33:$G52)-COUNTBLANK($G$33:$G52))</f>
-        <v/>
-      </c>
-      <c r="C52" s="1898">
-        <f>IF(입력!D70="","",입력!C70)</f>
-        <v/>
-      </c>
+      <c r="B52" s="830" t="str"/>
+      <c r="C52" s="1898" t="str"/>
       <c r="E52" s="1899" t="n"/>
-      <c r="F52" s="308">
-        <f>IF(C52="","",VLOOKUP(C52,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G52" s="902">
-        <f>IF(C52="","",입력!H70)</f>
-        <v/>
-      </c>
+      <c r="F52" s="308" t="str"/>
+      <c r="G52" s="902" t="str"/>
       <c r="I52" s="1904" t="n"/>
       <c r="J52" s="1881" t="n"/>
-      <c r="K52" s="1902">
-        <f>IF(G52="","",VLOOKUP(C52,입력!C66:G112,5,0))</f>
-        <v/>
-      </c>
+      <c r="K52" s="1902" t="str"/>
       <c r="L52" s="1899" t="n"/>
-      <c r="M52" s="829">
-        <f>IF(G52="","",VLOOKUP(C52,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P52" s="304">
-        <f>IF(C52="","",VLOOKUP(C52,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M52" s="829" t="str"/>
+      <c r="P52" s="304" t="str"/>
     </row>
     <row r="53" ht="19.9" customHeight="1" s="730">
-      <c r="B53" s="830">
-        <f>IF(C53="","",COUNTA($G$33:$G53)-COUNTBLANK($G$33:$G53))</f>
-        <v/>
-      </c>
-      <c r="C53" s="1898">
-        <f>IF(입력!D71="","",입력!C71)</f>
-        <v/>
-      </c>
+      <c r="B53" s="830" t="str"/>
+      <c r="C53" s="1898" t="str"/>
       <c r="E53" s="1899" t="n"/>
-      <c r="F53" s="308">
-        <f>IF(C53="","",VLOOKUP(C53,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G53" s="902">
-        <f>IF(C53="","",입력!H71)</f>
-        <v/>
-      </c>
+      <c r="F53" s="308" t="str"/>
+      <c r="G53" s="902" t="str"/>
       <c r="I53" s="1904" t="n"/>
       <c r="J53" s="1881" t="n"/>
-      <c r="K53" s="1902">
-        <f>IF(G53="","",VLOOKUP(C53,입력!C67:G113,5,0))</f>
-        <v/>
-      </c>
+      <c r="K53" s="1902" t="str"/>
       <c r="L53" s="1899" t="n"/>
-      <c r="M53" s="829">
-        <f>IF(G53="","",VLOOKUP(C53,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P53" s="304">
-        <f>IF(C53="","",VLOOKUP(C53,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M53" s="829" t="str"/>
+      <c r="P53" s="304" t="str"/>
     </row>
     <row r="54" ht="19.9" customHeight="1" s="730">
-      <c r="B54" s="830">
-        <f>IF(C54="","",COUNTA($G$33:$G54)-COUNTBLANK($G$33:$G54))</f>
-        <v/>
-      </c>
-      <c r="C54" s="1898">
-        <f>IF(입력!D72="","",입력!C72)</f>
-        <v/>
-      </c>
+      <c r="B54" s="830" t="str"/>
+      <c r="C54" s="1898" t="str"/>
       <c r="E54" s="1899" t="n"/>
-      <c r="F54" s="308">
-        <f>IF(C54="","",VLOOKUP(C54,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G54" s="902">
-        <f>IF(C54="","",입력!H72)</f>
-        <v/>
-      </c>
+      <c r="F54" s="308" t="str"/>
+      <c r="G54" s="902" t="str"/>
       <c r="I54" s="1904" t="n"/>
       <c r="J54" s="1881" t="n"/>
-      <c r="K54" s="1902">
-        <f>IF(G54="","",VLOOKUP(C54,입력!C68:G114,5,0))</f>
-        <v/>
-      </c>
+      <c r="K54" s="1902" t="str"/>
       <c r="L54" s="1899" t="n"/>
-      <c r="M54" s="829">
-        <f>IF(G54="","",VLOOKUP(C54,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P54" s="304">
-        <f>IF(C54="","",VLOOKUP(C54,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M54" s="829" t="str"/>
+      <c r="P54" s="304" t="str"/>
     </row>
     <row r="55" ht="19.9" customHeight="1" s="730">
-      <c r="B55" s="830">
-        <f>IF(C55="","",COUNTA($G$33:$G55)-COUNTBLANK($G$33:$G55))</f>
-        <v/>
-      </c>
-      <c r="C55" s="1898">
-        <f>IF(입력!D73="","",입력!C73)</f>
-        <v/>
-      </c>
+      <c r="B55" s="830" t="str"/>
+      <c r="C55" s="1898" t="str"/>
       <c r="E55" s="1899" t="n"/>
-      <c r="F55" s="308">
-        <f>IF(C55="","",VLOOKUP(C55,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G55" s="902">
-        <f>IF(C55="","",입력!H73)</f>
-        <v/>
-      </c>
+      <c r="F55" s="308" t="str"/>
+      <c r="G55" s="902" t="str"/>
       <c r="I55" s="1904" t="n"/>
       <c r="J55" s="1881" t="n"/>
-      <c r="K55" s="1902">
-        <f>IF(G55="","",VLOOKUP(C55,입력!C69:G115,5,0))</f>
-        <v/>
-      </c>
+      <c r="K55" s="1902" t="str"/>
       <c r="L55" s="1899" t="n"/>
-      <c r="M55" s="829">
-        <f>IF(G55="","",VLOOKUP(C55,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P55" s="304">
-        <f>IF(C55="","",VLOOKUP(C55,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M55" s="829" t="str"/>
+      <c r="P55" s="304" t="str"/>
     </row>
     <row r="56" ht="19.9" customHeight="1" s="730">
-      <c r="B56" s="830">
-        <f>IF(C56="","",COUNTA($G$33:$G56)-COUNTBLANK($G$33:$G56))</f>
-        <v/>
-      </c>
-      <c r="C56" s="1898">
-        <f>IF(입력!D74="","",입력!C74)</f>
-        <v/>
-      </c>
+      <c r="B56" s="830" t="str"/>
+      <c r="C56" s="1898" t="str"/>
       <c r="E56" s="1899" t="n"/>
-      <c r="F56" s="308">
-        <f>IF(C56="","",VLOOKUP(C56,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G56" s="902">
-        <f>IF(C56="","",입력!H74)</f>
-        <v/>
-      </c>
+      <c r="F56" s="308" t="str"/>
+      <c r="G56" s="902" t="str"/>
       <c r="I56" s="1904" t="n"/>
       <c r="J56" s="1881" t="n"/>
-      <c r="K56" s="1902">
-        <f>IF(G56="","",VLOOKUP(C56,입력!C70:G116,5,0))</f>
-        <v/>
-      </c>
+      <c r="K56" s="1902" t="str"/>
       <c r="L56" s="1899" t="n"/>
-      <c r="M56" s="829">
-        <f>IF(G56="","",VLOOKUP(C56,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P56" s="304">
-        <f>IF(C56="","",VLOOKUP(C56,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M56" s="829" t="str"/>
+      <c r="P56" s="304" t="str"/>
     </row>
     <row r="57" ht="19.9" customHeight="1" s="730">
-      <c r="B57" s="830">
-        <f>IF(C57="","",COUNTA($G$33:$G57)-COUNTBLANK($G$33:$G57))</f>
-        <v/>
-      </c>
-      <c r="C57" s="1898">
-        <f>IF(입력!D75="","",입력!C75)</f>
-        <v/>
-      </c>
+      <c r="B57" s="830" t="str"/>
+      <c r="C57" s="1898" t="str"/>
       <c r="E57" s="1899" t="n"/>
-      <c r="F57" s="308">
-        <f>IF(C57="","",VLOOKUP(C57,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G57" s="902">
-        <f>IF(C57="","",입력!H75)</f>
-        <v/>
-      </c>
+      <c r="F57" s="308" t="str"/>
+      <c r="G57" s="902" t="str"/>
       <c r="I57" s="1904" t="n"/>
       <c r="J57" s="1881" t="n"/>
-      <c r="K57" s="1902">
-        <f>IF(G57="","",VLOOKUP(C57,입력!C71:G117,5,0))</f>
-        <v/>
-      </c>
+      <c r="K57" s="1902" t="str"/>
       <c r="L57" s="1899" t="n"/>
-      <c r="M57" s="829">
-        <f>IF(G57="","",VLOOKUP(C57,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P57" s="304">
-        <f>IF(C57="","",VLOOKUP(C57,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M57" s="829" t="str"/>
+      <c r="P57" s="304" t="str"/>
     </row>
     <row r="58" ht="19.9" customHeight="1" s="730">
-      <c r="B58" s="830">
-        <f>IF(C58="","",COUNTA($G$33:$G58)-COUNTBLANK($G$33:$G58))</f>
-        <v/>
-      </c>
-      <c r="C58" s="1898">
-        <f>IF(입력!D76="","",입력!C76)</f>
-        <v/>
-      </c>
+      <c r="B58" s="830" t="str"/>
+      <c r="C58" s="1898" t="str"/>
       <c r="E58" s="1899" t="n"/>
-      <c r="F58" s="308">
-        <f>IF(C58="","",VLOOKUP(C58,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G58" s="902">
-        <f>IF(C58="","",입력!H76)</f>
-        <v/>
-      </c>
+      <c r="F58" s="308" t="str"/>
+      <c r="G58" s="902" t="str"/>
       <c r="I58" s="1904" t="n"/>
       <c r="J58" s="1881" t="n"/>
-      <c r="K58" s="1902">
-        <f>IF(G58="","",VLOOKUP(C58,입력!C72:G118,5,0))</f>
-        <v/>
-      </c>
+      <c r="K58" s="1902" t="str"/>
       <c r="L58" s="1899" t="n"/>
-      <c r="M58" s="829">
-        <f>IF(G58="","",VLOOKUP(C58,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P58" s="304">
-        <f>IF(C58="","",VLOOKUP(C58,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M58" s="829" t="str"/>
+      <c r="P58" s="304" t="str"/>
     </row>
     <row r="59" ht="19.9" customHeight="1" s="730">
-      <c r="B59" s="830">
-        <f>IF(C59="","",COUNTA($G$33:$G59)-COUNTBLANK($G$33:$G59))</f>
-        <v/>
-      </c>
-      <c r="C59" s="1898">
-        <f>IF(입력!D77="","",입력!C77)</f>
-        <v/>
-      </c>
+      <c r="B59" s="830" t="str"/>
+      <c r="C59" s="1898" t="str"/>
       <c r="E59" s="1899" t="n"/>
-      <c r="F59" s="308">
-        <f>IF(C59="","",VLOOKUP(C59,오염물질LIST!$B$4:$D$49,2,0))</f>
-        <v/>
-      </c>
-      <c r="G59" s="1012">
-        <f>IF(C59="","",입력!H77)</f>
-        <v/>
-      </c>
+      <c r="F59" s="308" t="str"/>
+      <c r="G59" s="1012" t="str"/>
       <c r="H59" s="1829" t="n"/>
       <c r="I59" s="1914" t="n"/>
       <c r="J59" s="1830" t="n"/>
-      <c r="K59" s="1915">
-        <f>IF(G59="","",VLOOKUP(C59,입력!C73:G119,5,0))</f>
-        <v/>
-      </c>
+      <c r="K59" s="1915" t="str"/>
       <c r="L59" s="1916" t="n"/>
-      <c r="M59" s="829">
-        <f>IF(G59="","",VLOOKUP(C59,오염물질LIST!$B$4:$D$49,3,0))</f>
-        <v/>
-      </c>
-      <c r="P59" s="304">
-        <f>IF(C59="","",VLOOKUP(C59,오염물질LIST!$B$4:$E$36,4,FALSE))</f>
-        <v/>
-      </c>
+      <c r="M59" s="829" t="str"/>
+      <c r="P59" s="304" t="str"/>
     </row>
     <row r="60" ht="20.1" customHeight="1" s="730">
       <c r="B60" s="1869" t="inlineStr">
@@ -20783,9 +20186,8 @@
         </is>
       </c>
       <c r="C60" s="1842" t="n"/>
-      <c r="D60" s="1917">
-        <f>입력!D27</f>
-        <v/>
+      <c r="D60" s="1917" t="n">
+        <v>0</v>
       </c>
       <c r="E60" s="1842" t="n"/>
       <c r="F60" s="1918" t="inlineStr">
@@ -20793,9 +20195,8 @@
           <t>~</t>
         </is>
       </c>
-      <c r="G60" s="1917">
-        <f>입력!D28</f>
-        <v/>
+      <c r="G60" s="1917" t="n">
+        <v>0</v>
       </c>
       <c r="H60" s="1842" t="n"/>
       <c r="I60" s="1845" t="inlineStr">
@@ -20804,9 +20205,10 @@
         </is>
       </c>
       <c r="J60" s="1835" t="n"/>
-      <c r="K60" s="1919">
-        <f>입력!D9</f>
-        <v/>
+      <c r="K60" s="1919" t="inlineStr">
+        <is>
+          <t>안우정</t>
+        </is>
       </c>
       <c r="L60" s="1837" t="n"/>
       <c r="M60" s="1837" t="n"/>
@@ -20826,9 +20228,10 @@
         </is>
       </c>
       <c r="J61" s="1835" t="n"/>
-      <c r="K61" s="1919">
-        <f>입력!E8</f>
-        <v/>
+      <c r="K61" s="1919" t="inlineStr">
+        <is>
+          <t>박종혁</t>
+        </is>
       </c>
       <c r="L61" s="1837" t="n"/>
       <c r="M61" s="1837" t="n"/>
